--- a/DATA/INTERPRETACION_RESULTADOS/Exp01-V3/resumen_experimento.xlsx
+++ b/DATA/INTERPRETACION_RESULTADOS/Exp01-V3/resumen_experimento.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,25 +441,60 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Accuracy_Temporal</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Precision_Temporal</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Recall_Temporal</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1_Temporal</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy_Prueba</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Precision_Prueba</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Recall_Prueba</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>F1_Prueba</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Especificidad</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy_Balanceada</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Estado_Oficial</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Conclusion</t>
         </is>
@@ -477,20 +512,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9226</v>
+        <v>0.8665</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5645</v>
+        <v>0.3895</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7292</v>
+        <v>0.7708</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6364</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Modelo con capacidad predictiva parcial.</t>
+        <v>0.5175</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9487</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Excelente</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>El modelo presenta un comportamiento favorable sobre la serie temporal y muestra capacidad prometedora para detectar eventos de la clase positiva. Se recomienda validación adicional antes de su utilización operacional.</t>
         </is>
       </c>
     </row>
